--- a/web/files/九龙-何文田-明寓.xlsx
+++ b/web/files/九龙-何文田-明寓.xlsx
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>128000000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>47076</v>
+        <v>47093</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>148000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>54372</v>
+        <v>54392</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>80000000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>29423</v>
+        <v>29433</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>85000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>31227</v>
+        <v>31239</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>108800000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>40015</v>
+        <v>40029</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>50856000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>38940</v>
+        <v>39000</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>42000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>32159</v>
+        <v>32209</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44988000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>34447</v>
+        <v>34500</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>48081000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>36815</v>
+        <v>36872</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>37359600</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>28606</v>
+        <v>28650</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>36935000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>28281</v>
+        <v>28324</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2035,17 +2035,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2722呎 (4+房)
+          <t>A | 2721呎 (4+房)
 $14800万
-$54,372/呎
+$54,392/呎
 (19年-02月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 2719呎 (4+房)
+          <t>B | 2718呎 (4+房)
 $12800万
-$47,076/呎
+$47,093/呎
 (19年-09月-09日)</t>
         </is>
       </c>
@@ -2058,17 +2058,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 2722呎 (4+房)
+          <t>A | 2721呎 (4+房)
 $8500万
-$31,227/呎
+$31,239/呎
 (24年-11月-29日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 2719呎 (4+房)
+          <t>B | 2718呎 (4+房)
 $8000万
-$29,423/呎
+$29,433/呎
 (26年-08月-03日)</t>
         </is>
       </c>
@@ -2089,9 +2089,9 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 2719呎 (4+房)
+          <t>B | 2718呎 (4+房)
 $10880万
-$40,015/呎
+$40,029/呎
 (19年-09月-26日)</t>
         </is>
       </c>
@@ -2112,9 +2112,9 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $5086万
-$38,940/呎
+$39,000/呎
 (19年-05月-14日)</t>
         </is>
       </c>
@@ -2135,9 +2135,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $4200万
-$32,159/呎
+$32,209/呎
 (20年-01月-08日)</t>
         </is>
       </c>
@@ -2158,9 +2158,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $4499万
-$34,447/呎
+$34,500/呎
 (19年-03月-07日)</t>
         </is>
       </c>
@@ -2181,9 +2181,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $4808万
-$36,815/呎
+$36,872/呎
 (18年-04月-20日)</t>
         </is>
       </c>
@@ -2204,9 +2204,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $3736万
-$28,606/呎
+$28,650/呎
 (18年-11月-05日)</t>
         </is>
       </c>
@@ -2227,9 +2227,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1306呎 (3房)
+          <t>B | 1304呎 (3房)
 $3694万
-$28,281/呎
+$28,324/呎
 (18年-11月-05日)</t>
         </is>
       </c>
